--- a/artfynd/A 38705-2026 artfynd.xlsx
+++ b/artfynd/A 38705-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136777178</v>
       </c>
       <c r="B2" t="n">
-        <v>96782</v>
+        <v>96784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136770618</v>
       </c>
       <c r="B3" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136772980</v>
       </c>
       <c r="B4" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136773509</v>
       </c>
       <c r="B5" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136771501</v>
       </c>
       <c r="B6" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>136769695</v>
       </c>
       <c r="B12" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>136772144</v>
       </c>
       <c r="B13" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>136772474</v>
       </c>
       <c r="B14" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>136769890</v>
       </c>
       <c r="B15" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 38705-2026 artfynd.xlsx
+++ b/artfynd/A 38705-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136777178</v>
       </c>
       <c r="B2" t="n">
-        <v>96784</v>
+        <v>96790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136770618</v>
       </c>
       <c r="B3" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136772980</v>
       </c>
       <c r="B4" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136773509</v>
       </c>
       <c r="B5" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136771501</v>
       </c>
       <c r="B6" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>136769695</v>
       </c>
       <c r="B12" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>136772144</v>
       </c>
       <c r="B13" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>136772474</v>
       </c>
       <c r="B14" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>136769890</v>
       </c>
       <c r="B15" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 38705-2026 artfynd.xlsx
+++ b/artfynd/A 38705-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136777178</v>
       </c>
       <c r="B2" t="n">
-        <v>96790</v>
+        <v>96792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136770618</v>
       </c>
       <c r="B3" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136772980</v>
       </c>
       <c r="B4" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136773509</v>
       </c>
       <c r="B5" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136771501</v>
       </c>
       <c r="B6" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>136769695</v>
       </c>
       <c r="B12" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>136772144</v>
       </c>
       <c r="B13" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>136772474</v>
       </c>
       <c r="B14" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>136769890</v>
       </c>
       <c r="B15" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 38705-2026 artfynd.xlsx
+++ b/artfynd/A 38705-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136777178</v>
       </c>
       <c r="B2" t="n">
-        <v>96792</v>
+        <v>96793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136770618</v>
       </c>
       <c r="B3" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136772980</v>
       </c>
       <c r="B4" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136773509</v>
       </c>
       <c r="B5" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136771501</v>
       </c>
       <c r="B6" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>136769695</v>
       </c>
       <c r="B12" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>136772144</v>
       </c>
       <c r="B13" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>136772474</v>
       </c>
       <c r="B14" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>136769890</v>
       </c>
       <c r="B15" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 38705-2026 artfynd.xlsx
+++ b/artfynd/A 38705-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136777178</v>
       </c>
       <c r="B2" t="n">
-        <v>96793</v>
+        <v>96799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136770618</v>
       </c>
       <c r="B3" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136772980</v>
       </c>
       <c r="B4" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136773509</v>
       </c>
       <c r="B5" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136771501</v>
       </c>
       <c r="B6" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>136769695</v>
       </c>
       <c r="B12" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>136772144</v>
       </c>
       <c r="B13" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>136772474</v>
       </c>
       <c r="B14" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>136769890</v>
       </c>
       <c r="B15" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 38705-2026 artfynd.xlsx
+++ b/artfynd/A 38705-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136777178</v>
       </c>
       <c r="B2" t="n">
-        <v>96799</v>
+        <v>96803</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136770618</v>
       </c>
       <c r="B3" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136772980</v>
       </c>
       <c r="B4" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136773509</v>
       </c>
       <c r="B5" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136771501</v>
       </c>
       <c r="B6" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>136769695</v>
       </c>
       <c r="B12" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>136772144</v>
       </c>
       <c r="B13" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>136772474</v>
       </c>
       <c r="B14" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>136769890</v>
       </c>
       <c r="B15" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 38705-2026 artfynd.xlsx
+++ b/artfynd/A 38705-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136777178</v>
       </c>
       <c r="B2" t="n">
-        <v>96803</v>
+        <v>96805</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136771501</v>
       </c>
       <c r="B6" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>136769695</v>
       </c>
       <c r="B12" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>136772144</v>
       </c>
       <c r="B13" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>136772474</v>
       </c>
       <c r="B14" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>136769890</v>
       </c>
       <c r="B15" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 38705-2026 artfynd.xlsx
+++ b/artfynd/A 38705-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136777178</v>
       </c>
       <c r="B2" t="n">
-        <v>96805</v>
+        <v>96807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136770618</v>
       </c>
       <c r="B3" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136772980</v>
       </c>
       <c r="B4" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136773509</v>
       </c>
       <c r="B5" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136771501</v>
       </c>
       <c r="B6" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>136769695</v>
       </c>
       <c r="B12" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>136772144</v>
       </c>
       <c r="B13" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>136772474</v>
       </c>
       <c r="B14" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>136769890</v>
       </c>
       <c r="B15" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 38705-2026 artfynd.xlsx
+++ b/artfynd/A 38705-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136777178</v>
       </c>
       <c r="B2" t="n">
-        <v>96807</v>
+        <v>96820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136770618</v>
       </c>
       <c r="B3" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136772980</v>
       </c>
       <c r="B4" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136773509</v>
       </c>
       <c r="B5" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136771501</v>
       </c>
       <c r="B6" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136770275</v>
       </c>
       <c r="B7" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136770661</v>
       </c>
       <c r="B10" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>136769695</v>
       </c>
       <c r="B12" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>136772144</v>
       </c>
       <c r="B13" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>136772474</v>
       </c>
       <c r="B14" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>136769890</v>
       </c>
       <c r="B15" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 38705-2026 artfynd.xlsx
+++ b/artfynd/A 38705-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136777178</v>
       </c>
       <c r="B2" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136770618</v>
       </c>
       <c r="B3" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136772980</v>
       </c>
       <c r="B4" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136773509</v>
       </c>
       <c r="B5" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136771501</v>
       </c>
       <c r="B6" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136770275</v>
       </c>
       <c r="B7" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136770661</v>
       </c>
       <c r="B10" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>136773117</v>
       </c>
       <c r="B11" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>136769695</v>
       </c>
       <c r="B12" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>136772144</v>
       </c>
       <c r="B13" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>136772474</v>
       </c>
       <c r="B14" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>136769890</v>
       </c>
       <c r="B15" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 38705-2026 artfynd.xlsx
+++ b/artfynd/A 38705-2026 artfynd.xlsx
@@ -1545,11 +1545,7 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gröndal, Gröndal, Sm</t>

--- a/artfynd/A 38705-2026 artfynd.xlsx
+++ b/artfynd/A 38705-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136777178</v>
       </c>
       <c r="B2" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136770618</v>
       </c>
       <c r="B3" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136772980</v>
       </c>
       <c r="B4" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136773509</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136771501</v>
       </c>
       <c r="B6" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>136769695</v>
       </c>
       <c r="B12" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>136772144</v>
       </c>
       <c r="B13" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>136772474</v>
       </c>
       <c r="B14" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>136769890</v>
       </c>
       <c r="B15" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 38705-2026 artfynd.xlsx
+++ b/artfynd/A 38705-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136777178</v>
       </c>
       <c r="B2" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136770618</v>
       </c>
       <c r="B3" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136772980</v>
       </c>
       <c r="B4" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136773509</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136771501</v>
       </c>
       <c r="B6" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136770275</v>
       </c>
       <c r="B7" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>136771764</v>
       </c>
       <c r="B8" t="n">
-        <v>6289</v>
+        <v>6295</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136773169</v>
       </c>
       <c r="B9" t="n">
-        <v>6289</v>
+        <v>6295</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136770661</v>
       </c>
       <c r="B10" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136773117</v>
       </c>
       <c r="B11" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>136769695</v>
       </c>
       <c r="B12" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>136772144</v>
       </c>
       <c r="B13" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>136772474</v>
       </c>
       <c r="B14" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>136769890</v>
       </c>
       <c r="B15" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 38705-2026 artfynd.xlsx
+++ b/artfynd/A 38705-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136777178</v>
       </c>
       <c r="B2" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136770618</v>
       </c>
       <c r="B3" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136772980</v>
       </c>
       <c r="B4" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136773509</v>
       </c>
       <c r="B5" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136771501</v>
       </c>
       <c r="B6" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>136769695</v>
       </c>
       <c r="B12" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>136772144</v>
       </c>
       <c r="B13" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>136772474</v>
       </c>
       <c r="B14" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>136769890</v>
       </c>
       <c r="B15" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 38705-2026 artfynd.xlsx
+++ b/artfynd/A 38705-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136777178</v>
       </c>
       <c r="B2" t="n">
-        <v>96836</v>
+        <v>96841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136770618</v>
       </c>
       <c r="B3" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136772980</v>
       </c>
       <c r="B4" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136773509</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136771501</v>
       </c>
       <c r="B6" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136770275</v>
       </c>
       <c r="B7" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136770661</v>
       </c>
       <c r="B10" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>136769695</v>
       </c>
       <c r="B12" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>136772144</v>
       </c>
       <c r="B13" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>136772474</v>
       </c>
       <c r="B14" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>136769890</v>
       </c>
       <c r="B15" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 38705-2026 artfynd.xlsx
+++ b/artfynd/A 38705-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136777178</v>
       </c>
       <c r="B2" t="n">
-        <v>96841</v>
+        <v>96843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136770618</v>
       </c>
       <c r="B3" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136772980</v>
       </c>
       <c r="B4" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136773509</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136771501</v>
       </c>
       <c r="B6" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>136769695</v>
       </c>
       <c r="B12" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>136772144</v>
       </c>
       <c r="B13" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>136772474</v>
       </c>
       <c r="B14" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>136769890</v>
       </c>
       <c r="B15" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
